--- a/log/excelFile.xlsx
+++ b/log/excelFile.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="92">
   <si>
     <t>2022-12-29 16:38:31,724</t>
   </si>
@@ -270,6 +270,21 @@
   </si>
   <si>
     <t xml:space="preserve"> 2025-03-20 22:00:25,674</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2025-04-14 15:53:31,216</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2025-04-14 17:16:27,738</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2025-04-14 17:16:31,439</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2025-04-14 17:37:19,928</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2025-04-14 17:37:23,443</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -317,7 +332,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1514,6 +1529,91 @@
       <c r="A71" t="s">
         <v>86</v>
       </c>
+      <c r="B71" t="s">
+        <v>1</v>
+      </c>
+      <c r="C71" t="s">
+        <v>2</v>
+      </c>
+      <c r="D71" t="s">
+        <v>3</v>
+      </c>
+      <c r="E71" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>87</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1</v>
+      </c>
+      <c r="C72" t="s">
+        <v>2</v>
+      </c>
+      <c r="D72" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>88</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1</v>
+      </c>
+      <c r="C73" t="s">
+        <v>2</v>
+      </c>
+      <c r="D73" t="s">
+        <v>3</v>
+      </c>
+      <c r="E73" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>89</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1</v>
+      </c>
+      <c r="C74" t="s">
+        <v>2</v>
+      </c>
+      <c r="D74" t="s">
+        <v>3</v>
+      </c>
+      <c r="E74" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>90</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1</v>
+      </c>
+      <c r="C75" t="s">
+        <v>2</v>
+      </c>
+      <c r="D75" t="s">
+        <v>3</v>
+      </c>
+      <c r="E75" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>91</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
